--- a/artfynd/A 26606-2026 artfynd.xlsx
+++ b/artfynd/A 26606-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134434136</v>
+        <v>134434137</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134434137</v>
+        <v>134434136</v>
       </c>
       <c r="B3" t="n">
-        <v>79123</v>
+        <v>79131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
